--- a/quote-template.xlsx
+++ b/quote-template.xlsx
@@ -823,7 +823,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: quote-maker-wine.vercel.app</t>
+      <t xml:space="preserve">: www.quickquote.kr</t>
     </r>
   </si>
 </sst>
